--- a/design_tables/excel/StatusConfig.xlsx
+++ b/design_tables/excel/StatusConfig.xlsx
@@ -85,21 +85,6 @@
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="StatusConfigTable" displayName="StatusConfigTable" ref="A1:G8" headerRowCount="1">
-  <x:tableColumns count="7">
-    <x:tableColumn id="1" name="id"/>
-    <x:tableColumn id="2" name="name"/>
-    <x:tableColumn id="3" name="type"/>
-    <x:tableColumn id="4" name="default_duration"/>
-    <x:tableColumn id="5" name="show_icon"/>
-    <x:tableColumn id="6" name="remove_condition"/>
-    <x:tableColumn id="7" name="comment"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -446,8 +431,5 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ed752b7a4f547f1"/>
-  </x:tableParts>
 </x:worksheet>
 </file>
--- a/design_tables/excel/StatusConfig.xlsx
+++ b/design_tables/excel/StatusConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StatusConfig" sheetId="1" r:id="R2781539bd8a04f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StatusConfig" sheetId="1" r:id="R6c891fbaad5c4d53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,13 +21,13 @@
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="FFFFFF"/>
+      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
       <x:b/>
       <x:sz val="11"/>
-      <x:color rgb="111827"/>
+      <x:color rgb="FF111827"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -40,17 +40,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="1F2937"/>
+        <x:fgColor rgb="FF1F2937"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="374151"/>
+        <x:fgColor rgb="FF374151"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="E5E7EB"/>
+        <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -270,125 +270,125 @@
     </x:row>
     <x:row r="2" ht="25.5" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>int</x:v>
+        <x:v>100001</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>变身状态</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>形态状态</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>直到魔力防御归零</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>bool</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>魔力防御 &lt;= 0</x:v>
       </x:c>
       <x:c r="G2" s="6" t="str">
-        <x:v>string</x:v>
+        <x:v>状态持有星光变身卡牌</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="25.5" customHeight="1">
       <x:c r="A3" s="9" t="str">
-        <x:v>状态ID</x:v>
+        <x:v>100002</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
-        <x:v>状态名称</x:v>
+        <x:v>高潮状态</x:v>
       </x:c>
       <x:c r="C3" s="9" t="str">
-        <x:v>状态类型</x:v>
+        <x:v>特殊状态</x:v>
       </x:c>
       <x:c r="D3" s="9" t="str">
-        <x:v>默认持续</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="E3" s="9" t="str">
-        <x:v>是否显示图标</x:v>
+        <x:v>true</x:v>
       </x:c>
       <x:c r="F3" s="9" t="str">
-        <x:v>移除条件</x:v>
+        <x:v>待定</x:v>
       </x:c>
       <x:c r="G3" s="9" t="str">
-        <x:v>说明</x:v>
+        <x:v>暂定强制结束当前玩家回合</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="25.5" customHeight="1">
-      <x:c r="A4" s="10" t="n">
-        <x:v>100001</x:v>
+      <x:c r="A4" s="10" t="str">
+        <x:v>100003</x:v>
       </x:c>
       <x:c r="B4" s="10" t="str">
-        <x:v>变身状态</x:v>
+        <x:v>力量</x:v>
       </x:c>
       <x:c r="C4" s="10" t="str">
-        <x:v>形态状态</x:v>
+        <x:v>战斗状态</x:v>
       </x:c>
       <x:c r="D4" s="10" t="str">
-        <x:v>直到魔力防御归零</x:v>
+        <x:v>本场战斗</x:v>
       </x:c>
       <x:c r="E4" s="10" t="str">
         <x:v>true</x:v>
       </x:c>
       <x:c r="F4" s="10" t="str">
-        <x:v>魔力防御 &lt;= 0</x:v>
+        <x:v>战斗结束</x:v>
       </x:c>
       <x:c r="G4" s="10" t="str">
-        <x:v>状态持有星光变身卡牌</x:v>
+        <x:v>提升造成的攻击伤害</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25.5" customHeight="1">
-      <x:c r="A5" s="10" t="n">
-        <x:v>100002</x:v>
+      <x:c r="A5" s="10" t="str">
+        <x:v>100004</x:v>
       </x:c>
       <x:c r="B5" s="10" t="str">
-        <x:v>高潮状态</x:v>
+        <x:v>易伤</x:v>
       </x:c>
       <x:c r="C5" s="10" t="str">
-        <x:v>特殊状态</x:v>
+        <x:v>战斗状态</x:v>
       </x:c>
       <x:c r="D5" s="10" t="str">
-        <x:v>待定</x:v>
+        <x:v>N回合</x:v>
       </x:c>
       <x:c r="E5" s="10" t="str">
         <x:v>true</x:v>
       </x:c>
       <x:c r="F5" s="10" t="str">
-        <x:v>待定</x:v>
+        <x:v>持续时间结束</x:v>
       </x:c>
       <x:c r="G5" s="10" t="str">
-        <x:v>暂定强制结束当前玩家回合</x:v>
+        <x:v>受到伤害增加</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="25.5" customHeight="1">
-      <x:c r="A6" s="10" t="n">
-        <x:v>100003</x:v>
+      <x:c r="A6" s="10" t="str">
+        <x:v>100005</x:v>
       </x:c>
       <x:c r="B6" s="10" t="str">
-        <x:v>力量</x:v>
+        <x:v>虚弱</x:v>
       </x:c>
       <x:c r="C6" s="10" t="str">
         <x:v>战斗状态</x:v>
       </x:c>
       <x:c r="D6" s="10" t="str">
-        <x:v>本场战斗</x:v>
+        <x:v>N回合</x:v>
       </x:c>
       <x:c r="E6" s="10" t="str">
         <x:v>true</x:v>
       </x:c>
       <x:c r="F6" s="10" t="str">
-        <x:v>战斗结束</x:v>
+        <x:v>持续时间结束</x:v>
       </x:c>
       <x:c r="G6" s="10" t="str">
-        <x:v>提升造成的攻击伤害</x:v>
+        <x:v>造成伤害降低</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="25.5" customHeight="1">
-      <x:c r="A7" s="10" t="n">
-        <x:v>100004</x:v>
+      <x:c r="A7" s="10" t="str">
+        <x:v>300003</x:v>
       </x:c>
       <x:c r="B7" s="10" t="str">
-        <x:v>易伤</x:v>
+        <x:v>眩晕</x:v>
       </x:c>
       <x:c r="C7" s="10" t="str">
         <x:v>战斗状态</x:v>
@@ -400,34 +400,20 @@
         <x:v>true</x:v>
       </x:c>
       <x:c r="F7" s="10" t="str">
-        <x:v>持续时间结束</x:v>
+        <x:v>回合开始时减少</x:v>
       </x:c>
       <x:c r="G7" s="10" t="str">
-        <x:v>受到伤害增加</x:v>
+        <x:v>跳过行动</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="25.5" customHeight="1">
-      <x:c r="A8" s="10" t="n">
-        <x:v>100005</x:v>
-      </x:c>
-      <x:c r="B8" s="10" t="str">
-        <x:v>虚弱</x:v>
-      </x:c>
-      <x:c r="C8" s="10" t="str">
-        <x:v>战斗状态</x:v>
-      </x:c>
-      <x:c r="D8" s="10" t="str">
-        <x:v>N回合</x:v>
-      </x:c>
-      <x:c r="E8" s="10" t="str">
-        <x:v>true</x:v>
-      </x:c>
-      <x:c r="F8" s="10" t="str">
-        <x:v>持续时间结束</x:v>
-      </x:c>
-      <x:c r="G8" s="10" t="str">
-        <x:v>造成伤害降低</x:v>
-      </x:c>
+      <x:c r="A8" s="10"/>
+      <x:c r="B8" s="10"/>
+      <x:c r="C8" s="10"/>
+      <x:c r="D8" s="10"/>
+      <x:c r="E8" s="10"/>
+      <x:c r="F8" s="10"/>
+      <x:c r="G8" s="10"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
